--- a/data/trans_orig/KIDM_C_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_C_1_R-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55718</t>
+          <t>55229</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113086</t>
+          <t>112680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119327</t>
+          <t>119605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5383</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>25418</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39885</t>
+          <t>39499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45549</t>
+          <t>45533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>11433</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>453</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>6697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>23604</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>40201</t>
+          <t>39347</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45717</t>
+          <t>45688</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66106</t>
+          <t>66739</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72592</t>
+          <t>72576</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>13183</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6192</t>
+          <t>6365</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50961</t>
+          <t>50321</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>60526</t>
+          <t>60594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71296</t>
+          <t>71377</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79508</t>
+          <t>79570</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>125609</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>138627</t>
+          <t>138454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6712</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>20753</t>
+          <t>19461</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14774</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>191806</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>204795</t>
+          <t>204302</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>251394</t>
+          <t>252686</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>265435</t>
+          <t>265844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>450122</t>
+          <t>449438</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>467845</t>
+          <t>467985</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
